--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.93760633641763</v>
+        <v>6.489861029667865</v>
       </c>
       <c r="D2" t="n">
-        <v>55.2508404677498</v>
+        <v>8.978261576009343</v>
       </c>
       <c r="E2" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F2" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.86894559600059</v>
+        <v>2.416203659350095</v>
       </c>
       <c r="D3" t="n">
-        <v>29.56914255033789</v>
+        <v>4.804985664429907</v>
       </c>
       <c r="E3" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F3" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.90924271735766</v>
+        <v>5.99775194157062</v>
       </c>
       <c r="D4" t="n">
-        <v>55.29388584024559</v>
+        <v>8.985256449039909</v>
       </c>
       <c r="E4" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.16551431248572</v>
+        <v>5.389396075778929</v>
       </c>
       <c r="D5" t="n">
-        <v>33.39614541143347</v>
+        <v>5.42687362935794</v>
       </c>
       <c r="E5" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F5" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.19690829040789</v>
+        <v>7.019497597191283</v>
       </c>
       <c r="D6" t="n">
-        <v>43.34216404381089</v>
+        <v>7.04310165711927</v>
       </c>
       <c r="E6" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F6" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.34927935759756</v>
+        <v>6.719257895609604</v>
       </c>
       <c r="D7" t="n">
-        <v>41.44176579403432</v>
+        <v>6.734286941530577</v>
       </c>
       <c r="E7" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F7" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.40386887547606</v>
+        <v>8.678128692264861</v>
       </c>
       <c r="D8" t="n">
-        <v>53.13349388964303</v>
+        <v>8.634192757066993</v>
       </c>
       <c r="E8" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F8" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>68.99507351160743</v>
+        <v>11.21169944563621</v>
       </c>
       <c r="D9" t="n">
-        <v>68.76917932215781</v>
+        <v>11.17499163985064</v>
       </c>
       <c r="E9" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F9" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.73578507176921</v>
+        <v>6.782065074162497</v>
       </c>
       <c r="D10" t="n">
-        <v>41.61332027862291</v>
+        <v>6.762164545276224</v>
       </c>
       <c r="E10" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F10" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>72.11262887038194</v>
+        <v>11.71830219143706</v>
       </c>
       <c r="D11" t="n">
-        <v>71.95578216640578</v>
+        <v>11.69281460204094</v>
       </c>
       <c r="E11" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F11" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.68806422022774</v>
+        <v>7.099310435787007</v>
       </c>
       <c r="D12" t="n">
-        <v>43.82992705971338</v>
+        <v>7.122363147203425</v>
       </c>
       <c r="E12" t="n">
-        <v>15.21534293670243</v>
+        <v>2.472493227214146</v>
       </c>
       <c r="F12" t="n">
-        <v>12.80926537657857</v>
+        <v>2.081505623694018</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
